--- a/data/trans_orig/P33B_R5-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R5-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>74100</t>
+          <t>80212</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60461</t>
+          <t>65669</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88868</t>
+          <t>95923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>200940</t>
+          <t>218810</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183556</t>
+          <t>199519</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>220597</t>
+          <t>239313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>275040</t>
+          <t>299022</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>252431</t>
+          <t>272615</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>302921</t>
+          <t>324722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>439842</t>
+          <t>497330</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>425074</t>
+          <t>481619</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453481</t>
+          <t>511873</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>551663</t>
+          <t>601909</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>532006</t>
+          <t>581406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>569047</t>
+          <t>621200</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>991504</t>
+          <t>1099239</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>963623</t>
+          <t>1073539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1014113</t>
+          <t>1125646</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752603</t>
+          <t>820719</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752603</t>
+          <t>820719</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752603</t>
+          <t>820719</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1266544</t>
+          <t>1398261</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1266544</t>
+          <t>1398261</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1266544</t>
+          <t>1398261</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>108930</t>
+          <t>119307</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74703</t>
+          <t>100616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133639</t>
+          <t>144613</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>175800</t>
+          <t>197616</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>129865</t>
+          <t>176965</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>205852</t>
+          <t>223155</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>284730</t>
+          <t>316924</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>228845</t>
+          <t>285931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>324619</t>
+          <t>349004</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2180367</t>
+          <t>2110178</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2155658</t>
+          <t>2084872</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2214594</t>
+          <t>2128869</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2061433</t>
+          <t>1973107</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2031381</t>
+          <t>1947568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2107368</t>
+          <t>1993758</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4241801</t>
+          <t>4083284</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4201912</t>
+          <t>4051204</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4297686</t>
+          <t>4114277</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237233</t>
+          <t>2170723</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237233</t>
+          <t>2170723</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237233</t>
+          <t>2170723</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4526531</t>
+          <t>4400208</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4526531</t>
+          <t>4400208</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4526531</t>
+          <t>4400208</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35886</t>
+          <t>38057</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25594</t>
+          <t>27002</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49579</t>
+          <t>51946</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>49618</t>
+          <t>56466</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>45804</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61612</t>
+          <t>69919</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>85504</t>
+          <t>94523</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70016</t>
+          <t>79194</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101651</t>
+          <t>113052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>610737</t>
+          <t>673530</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>597044</t>
+          <t>659641</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621029</t>
+          <t>684585</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>610845</t>
+          <t>678411</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>598851</t>
+          <t>664958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>621252</t>
+          <t>689073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1221582</t>
+          <t>1351941</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1205435</t>
+          <t>1333412</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1237070</t>
+          <t>1367270</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>218916</t>
+          <t>237576</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>169110</t>
+          <t>205966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>251578</t>
+          <t>266049</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>426358</t>
+          <t>472893</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>353161</t>
+          <t>436495</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>473021</t>
+          <t>506223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>645274</t>
+          <t>710469</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>551243</t>
+          <t>665372</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>701444</t>
+          <t>757387</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3230947</t>
+          <t>3281038</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3198285</t>
+          <t>3252565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3280753</t>
+          <t>3312648</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3223941</t>
+          <t>3253427</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3177278</t>
+          <t>3220097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3297138</t>
+          <t>3289825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6454887</t>
+          <t>6534464</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6398717</t>
+          <t>6487546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6548918</t>
+          <t>6579561</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3449863</t>
+          <t>3518614</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3449863</t>
+          <t>3518614</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3449863</t>
+          <t>3518614</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3650299</t>
+          <t>3726320</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3650299</t>
+          <t>3726320</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3650299</t>
+          <t>3726320</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7100161</t>
+          <t>7244933</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7100161</t>
+          <t>7244933</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7100161</t>
+          <t>7244933</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
